--- a/students.xlsx
+++ b/students.xlsx
@@ -28451,7 +28451,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>147203098</t>
+          <t>2608LPT031</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -28464,7 +28464,6 @@
           <t>202752073337</t>
         </is>
       </c>
-      <c r="F438" t="inlineStr"/>
       <c r="G438" t="inlineStr">
         <is>
           <t>FEMALE</t>
@@ -28475,7 +28474,11 @@
           <t>PGT ENGLISH</t>
         </is>
       </c>
-      <c r="I438" t="inlineStr"/>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>9765213553</t>
+        </is>
+      </c>
       <c r="J438" t="inlineStr">
         <is>
           <t>EMRS MELIAPUTTI, VILL-MELIAPUTTI, DIST.- SRIKAKULAM, 532215 AP</t>

--- a/students.xlsx
+++ b/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hallticket download\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0F89532-FCE5-4A9A-A2E7-3E9952720B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B252A451-CC25-4A31-BAF2-B0B0EE644818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6913,9 +6913,6 @@
     <t>TGT- ENGLISH</t>
   </si>
   <si>
-    <t>photos/p479.jpg</t>
-  </si>
-  <si>
     <t>photos/p480.JPEG</t>
   </si>
   <si>
@@ -6923,6 +6920,9 @@
   </si>
   <si>
     <t>SUDIP MONDAL</t>
+  </si>
+  <si>
+    <t>photos/p479.jpeg</t>
   </si>
 </sst>
 </file>
@@ -6980,55 +6980,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -13413,7 +13365,7 @@
         <v>28140208902</v>
       </c>
       <c r="N134" s="1" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="O134" s="1" t="s">
         <v>729</v>
@@ -24894,7 +24846,7 @@
         <v>2043</v>
       </c>
     </row>
-    <row r="390" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" s="1">
         <v>391</v>
       </c>
@@ -24905,7 +24857,7 @@
         <v>2044</v>
       </c>
       <c r="D390" s="1" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="E390" s="1">
         <v>934116972425</v>
@@ -25209,7 +25161,7 @@
         <v>2082</v>
       </c>
     </row>
-    <row r="397" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A397" s="1">
         <v>398</v>
       </c>
@@ -25248,7 +25200,7 @@
         <v>28120305828</v>
       </c>
       <c r="N397" s="1" t="s">
-        <v>2294</v>
+        <v>2297</v>
       </c>
       <c r="O397" s="1" t="s">
         <v>2087</v>
@@ -25625,7 +25577,7 @@
         <v>2130</v>
       </c>
       <c r="D406" s="1" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="E406" s="1">
         <v>478239648089</v>
@@ -27101,9 +27053,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:O438" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="2">
+    <filterColumn colId="1">
       <filters>
-        <filter val="2607LPT048"/>
+        <filter val="240404981"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O438">
@@ -27111,7 +27063,7 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/students.xlsx
+++ b/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hallticket download\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B252A451-CC25-4A31-BAF2-B0B0EE644818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CDF5C88-413E-46DD-9D9B-ABFFB2B2FF25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6913,9 +6913,6 @@
     <t>TGT- ENGLISH</t>
   </si>
   <si>
-    <t>photos/p480.JPEG</t>
-  </si>
-  <si>
     <t>PRASANT YADAV</t>
   </si>
   <si>
@@ -6923,6 +6920,9 @@
   </si>
   <si>
     <t>photos/p479.jpeg</t>
+  </si>
+  <si>
+    <t>photos/p480..jpeg</t>
   </si>
 </sst>
 </file>
@@ -13326,7 +13326,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>135</v>
       </c>
@@ -13365,7 +13365,7 @@
         <v>28140208902</v>
       </c>
       <c r="N134" s="1" t="s">
-        <v>2294</v>
+        <v>2297</v>
       </c>
       <c r="O134" s="1" t="s">
         <v>729</v>
@@ -24857,7 +24857,7 @@
         <v>2044</v>
       </c>
       <c r="D390" s="1" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="E390" s="1">
         <v>934116972425</v>
@@ -25161,7 +25161,7 @@
         <v>2082</v>
       </c>
     </row>
-    <row r="397" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" s="1">
         <v>398</v>
       </c>
@@ -25200,7 +25200,7 @@
         <v>28120305828</v>
       </c>
       <c r="N397" s="1" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="O397" s="1" t="s">
         <v>2087</v>
@@ -25577,7 +25577,7 @@
         <v>2130</v>
       </c>
       <c r="D406" s="1" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="E406" s="1">
         <v>478239648089</v>
@@ -27053,9 +27053,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:O438" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
+    <filterColumn colId="2">
       <filters>
-        <filter val="240404981"/>
+        <filter val="2602LPT061"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O438">

--- a/students.xlsx
+++ b/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hallticket download\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CDF5C88-413E-46DD-9D9B-ABFFB2B2FF25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEFF4555-9C6B-4C69-9D3B-7F9148EE4A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/students.xlsx
+++ b/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hallticket download\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEFF4555-9C6B-4C69-9D3B-7F9148EE4A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D7A57C-A2E5-4106-A556-770EFCD8719E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4366" uniqueCount="2298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4365" uniqueCount="2298">
   <si>
     <t>S.No.</t>
   </si>
@@ -6919,10 +6919,10 @@
     <t>SUDIP MONDAL</t>
   </si>
   <si>
-    <t>photos/p479.jpeg</t>
-  </si>
-  <si>
-    <t>photos/p480..jpeg</t>
+    <t>photos/p480.jpg</t>
+  </si>
+  <si>
+    <t>photos/p479.jpg</t>
   </si>
 </sst>
 </file>
@@ -13034,8 +13034,8 @@
       <c r="H127" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="I127" s="1" t="s">
-        <v>247</v>
+      <c r="I127" s="1">
+        <v>7986900177</v>
       </c>
       <c r="J127" s="1" t="s">
         <v>633</v>
@@ -13326,7 +13326,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>135</v>
       </c>
@@ -13365,7 +13365,7 @@
         <v>28140208902</v>
       </c>
       <c r="N134" s="1" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="O134" s="1" t="s">
         <v>729</v>
@@ -25161,7 +25161,7 @@
         <v>2082</v>
       </c>
     </row>
-    <row r="397" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A397" s="1">
         <v>398</v>
       </c>
@@ -25200,7 +25200,7 @@
         <v>28120305828</v>
       </c>
       <c r="N397" s="1" t="s">
-        <v>2296</v>
+        <v>2297</v>
       </c>
       <c r="O397" s="1" t="s">
         <v>2087</v>
@@ -27055,7 +27055,7 @@
   <autoFilter ref="A1:O438" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="2">
       <filters>
-        <filter val="2602LPT061"/>
+        <filter val="2607LPT055"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O438">

--- a/students.xlsx
+++ b/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hallticket download\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCB52B3C-DFF2-49C9-AFD9-776BC21F549A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFFD86FA-B017-4F07-8359-7017E9D632D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6775,9 +6775,6 @@
     <t>2608LPT023</t>
   </si>
   <si>
-    <t>VIKAS KUMAR YADAV</t>
-  </si>
-  <si>
     <t>7408366152</t>
   </si>
   <si>
@@ -6920,6 +6917,9 @@
   </si>
   <si>
     <t>photos/p479.jpg</t>
+  </si>
+  <si>
+    <t>VIKAS KUMAR CHAURASIA</t>
   </si>
 </sst>
 </file>
@@ -7322,6 +7322,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:N438"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7381,7 +7382,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -7425,7 +7426,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -7469,7 +7470,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -7513,7 +7514,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -7557,7 +7558,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -7601,7 +7602,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -7645,7 +7646,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -7689,7 +7690,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -7733,7 +7734,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -7777,7 +7778,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -7821,7 +7822,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -7865,7 +7866,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -7909,7 +7910,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -7953,7 +7954,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -7997,7 +7998,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -8041,7 +8042,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -8085,7 +8086,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -8129,7 +8130,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -8173,7 +8174,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -8217,7 +8218,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -8261,7 +8262,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -8305,7 +8306,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -8349,7 +8350,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -8393,7 +8394,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -8437,7 +8438,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -8481,7 +8482,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -8525,7 +8526,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -8545,7 +8546,7 @@
         <v>16</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>2292</v>
+        <v>2291</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>174</v>
@@ -8569,7 +8570,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -8613,7 +8614,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -8657,7 +8658,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -8701,7 +8702,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -8745,7 +8746,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -8789,7 +8790,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -8833,7 +8834,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -8877,7 +8878,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -8921,7 +8922,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -8965,7 +8966,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -9009,7 +9010,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -9053,7 +9054,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -9097,7 +9098,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -9141,7 +9142,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -9185,7 +9186,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -9229,7 +9230,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -9273,7 +9274,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -9317,7 +9318,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -9361,7 +9362,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -9405,7 +9406,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -9449,7 +9450,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -9493,7 +9494,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -9537,7 +9538,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -9581,7 +9582,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -9625,7 +9626,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -9669,7 +9670,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -9713,7 +9714,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -9757,7 +9758,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -9801,7 +9802,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -9845,7 +9846,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -9889,7 +9890,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -9933,7 +9934,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -9977,7 +9978,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -10021,7 +10022,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -10065,7 +10066,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -10109,7 +10110,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -10153,7 +10154,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -10197,7 +10198,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -10241,7 +10242,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -10285,7 +10286,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -10329,7 +10330,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -10373,7 +10374,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -10417,7 +10418,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -10461,7 +10462,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -10505,7 +10506,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -10549,7 +10550,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -10593,7 +10594,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -10637,7 +10638,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -10681,7 +10682,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -10725,7 +10726,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -10769,7 +10770,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -10813,7 +10814,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -10857,7 +10858,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -10901,7 +10902,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -10945,7 +10946,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -10989,7 +10990,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>84</v>
       </c>
@@ -11033,7 +11034,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>85</v>
       </c>
@@ -11077,7 +11078,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>86</v>
       </c>
@@ -11121,7 +11122,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>87</v>
       </c>
@@ -11165,7 +11166,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>89</v>
       </c>
@@ -11209,7 +11210,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>90</v>
       </c>
@@ -11253,7 +11254,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>91</v>
       </c>
@@ -11297,7 +11298,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>92</v>
       </c>
@@ -11341,7 +11342,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>93</v>
       </c>
@@ -11385,7 +11386,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>94</v>
       </c>
@@ -11429,7 +11430,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>95</v>
       </c>
@@ -11473,7 +11474,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>96</v>
       </c>
@@ -11517,7 +11518,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>97</v>
       </c>
@@ -11561,7 +11562,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>98</v>
       </c>
@@ -11605,7 +11606,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>99</v>
       </c>
@@ -11649,7 +11650,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>100</v>
       </c>
@@ -11693,7 +11694,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>101</v>
       </c>
@@ -11737,7 +11738,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>102</v>
       </c>
@@ -11781,7 +11782,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>103</v>
       </c>
@@ -11825,7 +11826,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>104</v>
       </c>
@@ -11869,7 +11870,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>105</v>
       </c>
@@ -11913,7 +11914,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>106</v>
       </c>
@@ -11957,7 +11958,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>107</v>
       </c>
@@ -12001,7 +12002,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>108</v>
       </c>
@@ -12045,7 +12046,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>109</v>
       </c>
@@ -12089,7 +12090,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>110</v>
       </c>
@@ -12133,7 +12134,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>111</v>
       </c>
@@ -12177,7 +12178,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>112</v>
       </c>
@@ -12221,7 +12222,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>113</v>
       </c>
@@ -12265,7 +12266,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>114</v>
       </c>
@@ -12309,7 +12310,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>115</v>
       </c>
@@ -12353,7 +12354,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>116</v>
       </c>
@@ -12397,7 +12398,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>117</v>
       </c>
@@ -12441,7 +12442,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>118</v>
       </c>
@@ -12485,7 +12486,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>119</v>
       </c>
@@ -12529,7 +12530,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>120</v>
       </c>
@@ -12573,7 +12574,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>121</v>
       </c>
@@ -12617,7 +12618,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>122</v>
       </c>
@@ -12661,7 +12662,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>123</v>
       </c>
@@ -12705,7 +12706,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>124</v>
       </c>
@@ -12749,7 +12750,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>125</v>
       </c>
@@ -12793,7 +12794,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>126</v>
       </c>
@@ -12837,7 +12838,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>127</v>
       </c>
@@ -12881,7 +12882,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>128</v>
       </c>
@@ -12925,7 +12926,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>129</v>
       </c>
@@ -12969,7 +12970,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>130</v>
       </c>
@@ -13013,7 +13014,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>131</v>
       </c>
@@ -13057,7 +13058,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>132</v>
       </c>
@@ -13101,7 +13102,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>133</v>
       </c>
@@ -13145,7 +13146,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>134</v>
       </c>
@@ -13189,7 +13190,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>135</v>
       </c>
@@ -13227,13 +13228,13 @@
         <v>28140208902</v>
       </c>
       <c r="M134" s="1" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="N134" s="1" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>136</v>
       </c>
@@ -13277,7 +13278,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>137</v>
       </c>
@@ -13321,7 +13322,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>138</v>
       </c>
@@ -13365,7 +13366,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>139</v>
       </c>
@@ -13409,7 +13410,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>140</v>
       </c>
@@ -13453,7 +13454,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>141</v>
       </c>
@@ -13497,7 +13498,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>142</v>
       </c>
@@ -13541,7 +13542,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>143</v>
       </c>
@@ -13585,7 +13586,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>144</v>
       </c>
@@ -13629,7 +13630,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>145</v>
       </c>
@@ -13673,7 +13674,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>146</v>
       </c>
@@ -13717,7 +13718,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>147</v>
       </c>
@@ -13761,7 +13762,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>148</v>
       </c>
@@ -13805,7 +13806,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>149</v>
       </c>
@@ -13849,7 +13850,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>150</v>
       </c>
@@ -13893,7 +13894,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>151</v>
       </c>
@@ -13937,7 +13938,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>152</v>
       </c>
@@ -13981,7 +13982,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>153</v>
       </c>
@@ -14025,7 +14026,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>154</v>
       </c>
@@ -14069,7 +14070,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>155</v>
       </c>
@@ -14113,7 +14114,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>156</v>
       </c>
@@ -14157,7 +14158,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>157</v>
       </c>
@@ -14201,7 +14202,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>158</v>
       </c>
@@ -14245,7 +14246,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>159</v>
       </c>
@@ -14289,7 +14290,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>160</v>
       </c>
@@ -14333,7 +14334,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>161</v>
       </c>
@@ -14377,7 +14378,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>162</v>
       </c>
@@ -14421,7 +14422,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>163</v>
       </c>
@@ -14465,7 +14466,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>164</v>
       </c>
@@ -14509,7 +14510,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>165</v>
       </c>
@@ -14553,7 +14554,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>166</v>
       </c>
@@ -14594,10 +14595,10 @@
         <v>902</v>
       </c>
       <c r="N165" s="1" t="s">
-        <v>2290</v>
-      </c>
-    </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="166" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>167</v>
       </c>
@@ -14641,7 +14642,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>168</v>
       </c>
@@ -14682,10 +14683,10 @@
         <v>911</v>
       </c>
       <c r="N167" s="1" t="s">
-        <v>2291</v>
-      </c>
-    </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.3">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="168" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>169</v>
       </c>
@@ -14729,7 +14730,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>170</v>
       </c>
@@ -14773,7 +14774,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>171</v>
       </c>
@@ -14817,7 +14818,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>172</v>
       </c>
@@ -14861,7 +14862,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>173</v>
       </c>
@@ -14905,7 +14906,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>174</v>
       </c>
@@ -14949,7 +14950,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>175</v>
       </c>
@@ -14993,7 +14994,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>176</v>
       </c>
@@ -15037,7 +15038,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>177</v>
       </c>
@@ -15081,7 +15082,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>178</v>
       </c>
@@ -15125,7 +15126,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>179</v>
       </c>
@@ -15169,7 +15170,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>180</v>
       </c>
@@ -15213,7 +15214,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>181</v>
       </c>
@@ -15257,7 +15258,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>182</v>
       </c>
@@ -15301,7 +15302,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>183</v>
       </c>
@@ -15345,7 +15346,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>184</v>
       </c>
@@ -15389,7 +15390,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>185</v>
       </c>
@@ -15433,7 +15434,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>186</v>
       </c>
@@ -15477,7 +15478,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>187</v>
       </c>
@@ -15521,7 +15522,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>188</v>
       </c>
@@ -15565,7 +15566,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>189</v>
       </c>
@@ -15609,7 +15610,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>190</v>
       </c>
@@ -15653,7 +15654,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>191</v>
       </c>
@@ -15697,7 +15698,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>192</v>
       </c>
@@ -15741,7 +15742,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>193</v>
       </c>
@@ -15785,7 +15786,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>194</v>
       </c>
@@ -15829,7 +15830,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>195</v>
       </c>
@@ -15873,7 +15874,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>196</v>
       </c>
@@ -15917,7 +15918,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>197</v>
       </c>
@@ -15961,7 +15962,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>198</v>
       </c>
@@ -16005,7 +16006,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>199</v>
       </c>
@@ -16049,7 +16050,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>200</v>
       </c>
@@ -16093,7 +16094,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>201</v>
       </c>
@@ -16137,7 +16138,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>202</v>
       </c>
@@ -16181,7 +16182,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>203</v>
       </c>
@@ -16225,7 +16226,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>204</v>
       </c>
@@ -16269,7 +16270,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>205</v>
       </c>
@@ -16313,7 +16314,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>206</v>
       </c>
@@ -16357,7 +16358,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
         <v>207</v>
       </c>
@@ -16401,7 +16402,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
         <v>208</v>
       </c>
@@ -16445,7 +16446,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
         <v>209</v>
       </c>
@@ -16489,7 +16490,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
         <v>210</v>
       </c>
@@ -16533,7 +16534,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>211</v>
       </c>
@@ -16577,7 +16578,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>212</v>
       </c>
@@ -16621,7 +16622,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
         <v>213</v>
       </c>
@@ -16665,7 +16666,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>214</v>
       </c>
@@ -16709,7 +16710,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>215</v>
       </c>
@@ -16753,7 +16754,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
         <v>216</v>
       </c>
@@ -16797,7 +16798,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
         <v>217</v>
       </c>
@@ -16841,7 +16842,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
         <v>218</v>
       </c>
@@ -16885,7 +16886,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <v>219</v>
       </c>
@@ -16929,7 +16930,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
         <v>220</v>
       </c>
@@ -16973,7 +16974,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
         <v>221</v>
       </c>
@@ -17017,7 +17018,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
         <v>222</v>
       </c>
@@ -17061,7 +17062,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
         <v>223</v>
       </c>
@@ -17105,7 +17106,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>224</v>
       </c>
@@ -17149,7 +17150,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>225</v>
       </c>
@@ -17193,7 +17194,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
         <v>226</v>
       </c>
@@ -17237,7 +17238,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
         <v>227</v>
       </c>
@@ -17281,7 +17282,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
         <v>228</v>
       </c>
@@ -17325,7 +17326,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="1">
         <v>229</v>
       </c>
@@ -17369,7 +17370,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="1">
         <v>230</v>
       </c>
@@ -17413,7 +17414,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
         <v>231</v>
       </c>
@@ -17457,7 +17458,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
         <v>232</v>
       </c>
@@ -17501,7 +17502,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
         <v>233</v>
       </c>
@@ -17545,7 +17546,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
         <v>234</v>
       </c>
@@ -17589,7 +17590,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
         <v>235</v>
       </c>
@@ -17633,7 +17634,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
         <v>236</v>
       </c>
@@ -17677,7 +17678,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
         <v>237</v>
       </c>
@@ -17721,7 +17722,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
         <v>238</v>
       </c>
@@ -17765,7 +17766,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
         <v>239</v>
       </c>
@@ -17809,7 +17810,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
         <v>240</v>
       </c>
@@ -17853,7 +17854,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
         <v>241</v>
       </c>
@@ -17897,7 +17898,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
         <v>242</v>
       </c>
@@ -17941,7 +17942,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="1">
         <v>243</v>
       </c>
@@ -17985,7 +17986,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="1">
         <v>244</v>
       </c>
@@ -18029,7 +18030,7 @@
         <v>1296</v>
       </c>
     </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="1">
         <v>245</v>
       </c>
@@ -18073,7 +18074,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="1">
         <v>246</v>
       </c>
@@ -18117,7 +18118,7 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="1">
         <v>247</v>
       </c>
@@ -18161,7 +18162,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="1">
         <v>248</v>
       </c>
@@ -18205,7 +18206,7 @@
         <v>1316</v>
       </c>
     </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="1">
         <v>249</v>
       </c>
@@ -18249,7 +18250,7 @@
         <v>1322</v>
       </c>
     </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="1">
         <v>250</v>
       </c>
@@ -18293,7 +18294,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="1">
         <v>251</v>
       </c>
@@ -18337,7 +18338,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="1">
         <v>252</v>
       </c>
@@ -18381,7 +18382,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
         <v>253</v>
       </c>
@@ -18425,7 +18426,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
         <v>254</v>
       </c>
@@ -18469,7 +18470,7 @@
         <v>1345</v>
       </c>
     </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
         <v>255</v>
       </c>
@@ -18513,7 +18514,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
         <v>256</v>
       </c>
@@ -18557,7 +18558,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="1">
         <v>257</v>
       </c>
@@ -18601,7 +18602,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
         <v>258</v>
       </c>
@@ -18645,7 +18646,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="1">
         <v>259</v>
       </c>
@@ -18689,7 +18690,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
         <v>260</v>
       </c>
@@ -18733,7 +18734,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
         <v>261</v>
       </c>
@@ -18777,7 +18778,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="1">
         <v>262</v>
       </c>
@@ -18821,7 +18822,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="1">
         <v>263</v>
       </c>
@@ -18865,7 +18866,7 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
         <v>264</v>
       </c>
@@ -18909,7 +18910,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="1">
         <v>265</v>
       </c>
@@ -18953,7 +18954,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="1">
         <v>266</v>
       </c>
@@ -18997,7 +18998,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" s="1">
         <v>267</v>
       </c>
@@ -19041,7 +19042,7 @@
         <v>1410</v>
       </c>
     </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" s="1">
         <v>268</v>
       </c>
@@ -19085,7 +19086,7 @@
         <v>1414</v>
       </c>
     </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" s="1">
         <v>269</v>
       </c>
@@ -19129,7 +19130,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="1">
         <v>270</v>
       </c>
@@ -19173,7 +19174,7 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="1">
         <v>271</v>
       </c>
@@ -19217,7 +19218,7 @@
         <v>1429</v>
       </c>
     </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="1">
         <v>272</v>
       </c>
@@ -19261,7 +19262,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="1">
         <v>273</v>
       </c>
@@ -19305,7 +19306,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" s="1">
         <v>274</v>
       </c>
@@ -19349,7 +19350,7 @@
         <v>1442</v>
       </c>
     </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" s="1">
         <v>275</v>
       </c>
@@ -19393,7 +19394,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" s="1">
         <v>276</v>
       </c>
@@ -19437,7 +19438,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" s="1">
         <v>277</v>
       </c>
@@ -19481,7 +19482,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" s="1">
         <v>278</v>
       </c>
@@ -19525,7 +19526,7 @@
         <v>1461</v>
       </c>
     </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" s="1">
         <v>279</v>
       </c>
@@ -19569,7 +19570,7 @@
         <v>1466</v>
       </c>
     </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" s="1">
         <v>280</v>
       </c>
@@ -19613,7 +19614,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" s="1">
         <v>281</v>
       </c>
@@ -19657,7 +19658,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" s="1">
         <v>282</v>
       </c>
@@ -19701,7 +19702,7 @@
         <v>1479</v>
       </c>
     </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" s="1">
         <v>283</v>
       </c>
@@ -19745,7 +19746,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" s="1">
         <v>284</v>
       </c>
@@ -19789,7 +19790,7 @@
         <v>1489</v>
       </c>
     </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" s="1">
         <v>285</v>
       </c>
@@ -19833,7 +19834,7 @@
         <v>1494</v>
       </c>
     </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" s="1">
         <v>286</v>
       </c>
@@ -19877,7 +19878,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" s="1">
         <v>287</v>
       </c>
@@ -19921,7 +19922,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" s="1">
         <v>288</v>
       </c>
@@ -19965,7 +19966,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" s="1">
         <v>289</v>
       </c>
@@ -20009,7 +20010,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" s="1">
         <v>290</v>
       </c>
@@ -20053,7 +20054,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" s="1">
         <v>291</v>
       </c>
@@ -20097,7 +20098,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="291" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" s="1">
         <v>292</v>
       </c>
@@ -20141,7 +20142,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="292" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" s="1">
         <v>293</v>
       </c>
@@ -20185,7 +20186,7 @@
         <v>1533</v>
       </c>
     </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" s="1">
         <v>294</v>
       </c>
@@ -20229,7 +20230,7 @@
         <v>1538</v>
       </c>
     </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="1">
         <v>295</v>
       </c>
@@ -20273,7 +20274,7 @@
         <v>1543</v>
       </c>
     </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="1">
         <v>296</v>
       </c>
@@ -20317,7 +20318,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
         <v>297</v>
       </c>
@@ -20361,7 +20362,7 @@
         <v>1553</v>
       </c>
     </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
         <v>298</v>
       </c>
@@ -20405,7 +20406,7 @@
         <v>1558</v>
       </c>
     </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" s="1">
         <v>299</v>
       </c>
@@ -20449,7 +20450,7 @@
         <v>1563</v>
       </c>
     </row>
-    <row r="299" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" s="1">
         <v>300</v>
       </c>
@@ -20493,7 +20494,7 @@
         <v>1568</v>
       </c>
     </row>
-    <row r="300" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" s="1">
         <v>301</v>
       </c>
@@ -20537,7 +20538,7 @@
         <v>1573</v>
       </c>
     </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="1">
         <v>302</v>
       </c>
@@ -20581,7 +20582,7 @@
         <v>1578</v>
       </c>
     </row>
-    <row r="302" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" s="1">
         <v>303</v>
       </c>
@@ -20625,7 +20626,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="1">
         <v>304</v>
       </c>
@@ -20669,7 +20670,7 @@
         <v>1588</v>
       </c>
     </row>
-    <row r="304" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" s="1">
         <v>305</v>
       </c>
@@ -20713,7 +20714,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="305" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" s="1">
         <v>306</v>
       </c>
@@ -20757,7 +20758,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="306" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" s="1">
         <v>307</v>
       </c>
@@ -20801,7 +20802,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="307" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" s="1">
         <v>308</v>
       </c>
@@ -20845,7 +20846,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="308" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" s="1">
         <v>309</v>
       </c>
@@ -20889,7 +20890,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="1">
         <v>310</v>
       </c>
@@ -20933,7 +20934,7 @@
         <v>1624</v>
       </c>
     </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" s="1">
         <v>311</v>
       </c>
@@ -20977,7 +20978,7 @@
         <v>1630</v>
       </c>
     </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" s="1">
         <v>312</v>
       </c>
@@ -21021,7 +21022,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" s="1">
         <v>313</v>
       </c>
@@ -21065,7 +21066,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" s="1">
         <v>314</v>
       </c>
@@ -21109,7 +21110,7 @@
         <v>1648</v>
       </c>
     </row>
-    <row r="314" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" s="1">
         <v>315</v>
       </c>
@@ -21153,7 +21154,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="315" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" s="1">
         <v>316</v>
       </c>
@@ -21197,7 +21198,7 @@
         <v>1660</v>
       </c>
     </row>
-    <row r="316" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" s="1">
         <v>317</v>
       </c>
@@ -21241,7 +21242,7 @@
         <v>1665</v>
       </c>
     </row>
-    <row r="317" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" s="1">
         <v>318</v>
       </c>
@@ -21285,7 +21286,7 @@
         <v>1670</v>
       </c>
     </row>
-    <row r="318" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" s="1">
         <v>319</v>
       </c>
@@ -21329,7 +21330,7 @@
         <v>1675</v>
       </c>
     </row>
-    <row r="319" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" s="1">
         <v>320</v>
       </c>
@@ -21373,7 +21374,7 @@
         <v>1680</v>
       </c>
     </row>
-    <row r="320" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" s="1">
         <v>321</v>
       </c>
@@ -21417,7 +21418,7 @@
         <v>1685</v>
       </c>
     </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" s="1">
         <v>322</v>
       </c>
@@ -21461,7 +21462,7 @@
         <v>1690</v>
       </c>
     </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" s="1">
         <v>323</v>
       </c>
@@ -21505,7 +21506,7 @@
         <v>1695</v>
       </c>
     </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" s="1">
         <v>324</v>
       </c>
@@ -21549,7 +21550,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" s="1">
         <v>325</v>
       </c>
@@ -21593,7 +21594,7 @@
         <v>1705</v>
       </c>
     </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" s="1">
         <v>326</v>
       </c>
@@ -21637,7 +21638,7 @@
         <v>1711</v>
       </c>
     </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" s="1">
         <v>327</v>
       </c>
@@ -21681,7 +21682,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" s="1">
         <v>328</v>
       </c>
@@ -21725,7 +21726,7 @@
         <v>1723</v>
       </c>
     </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" s="1">
         <v>329</v>
       </c>
@@ -21769,7 +21770,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" s="1">
         <v>330</v>
       </c>
@@ -21813,7 +21814,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" s="1">
         <v>331</v>
       </c>
@@ -21857,7 +21858,7 @@
         <v>1741</v>
       </c>
     </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" s="1">
         <v>332</v>
       </c>
@@ -21901,7 +21902,7 @@
         <v>1747</v>
       </c>
     </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" s="1">
         <v>333</v>
       </c>
@@ -21945,7 +21946,7 @@
         <v>1753</v>
       </c>
     </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" s="1">
         <v>334</v>
       </c>
@@ -21989,7 +21990,7 @@
         <v>1759</v>
       </c>
     </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" s="1">
         <v>335</v>
       </c>
@@ -22033,7 +22034,7 @@
         <v>1765</v>
       </c>
     </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" s="1">
         <v>336</v>
       </c>
@@ -22077,7 +22078,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" s="1">
         <v>337</v>
       </c>
@@ -22121,7 +22122,7 @@
         <v>1776</v>
       </c>
     </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" s="1">
         <v>338</v>
       </c>
@@ -22165,7 +22166,7 @@
         <v>1782</v>
       </c>
     </row>
-    <row r="338" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" s="1">
         <v>339</v>
       </c>
@@ -22209,7 +22210,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="339" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" s="1">
         <v>340</v>
       </c>
@@ -22253,7 +22254,7 @@
         <v>1792</v>
       </c>
     </row>
-    <row r="340" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" s="1">
         <v>341</v>
       </c>
@@ -22297,7 +22298,7 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="341" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" s="1">
         <v>342</v>
       </c>
@@ -22341,7 +22342,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="342" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" s="1">
         <v>343</v>
       </c>
@@ -22385,7 +22386,7 @@
         <v>1808</v>
       </c>
     </row>
-    <row r="343" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" s="1">
         <v>344</v>
       </c>
@@ -22429,7 +22430,7 @@
         <v>1815</v>
       </c>
     </row>
-    <row r="344" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" s="1">
         <v>345</v>
       </c>
@@ -22473,7 +22474,7 @@
         <v>1820</v>
       </c>
     </row>
-    <row r="345" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" s="1">
         <v>346</v>
       </c>
@@ -22517,7 +22518,7 @@
         <v>1825</v>
       </c>
     </row>
-    <row r="346" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" s="1">
         <v>347</v>
       </c>
@@ -22561,7 +22562,7 @@
         <v>1830</v>
       </c>
     </row>
-    <row r="347" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" s="1">
         <v>348</v>
       </c>
@@ -22605,7 +22606,7 @@
         <v>1834</v>
       </c>
     </row>
-    <row r="348" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" s="1">
         <v>349</v>
       </c>
@@ -22649,7 +22650,7 @@
         <v>1839</v>
       </c>
     </row>
-    <row r="349" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" s="1">
         <v>350</v>
       </c>
@@ -22693,7 +22694,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="350" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" s="1">
         <v>351</v>
       </c>
@@ -22737,7 +22738,7 @@
         <v>1849</v>
       </c>
     </row>
-    <row r="351" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" s="1">
         <v>352</v>
       </c>
@@ -22781,7 +22782,7 @@
         <v>1854</v>
       </c>
     </row>
-    <row r="352" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" s="1">
         <v>353</v>
       </c>
@@ -22825,7 +22826,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="353" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" s="1">
         <v>354</v>
       </c>
@@ -22869,7 +22870,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="354" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" s="1">
         <v>355</v>
       </c>
@@ -22913,7 +22914,7 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="355" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" s="1">
         <v>356</v>
       </c>
@@ -22957,7 +22958,7 @@
         <v>1874</v>
       </c>
     </row>
-    <row r="356" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" s="1">
         <v>357</v>
       </c>
@@ -23001,7 +23002,7 @@
         <v>1877</v>
       </c>
     </row>
-    <row r="357" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" s="1">
         <v>358</v>
       </c>
@@ -23045,7 +23046,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="358" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" s="1">
         <v>359</v>
       </c>
@@ -23089,7 +23090,7 @@
         <v>1888</v>
       </c>
     </row>
-    <row r="359" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" s="1">
         <v>360</v>
       </c>
@@ -23133,7 +23134,7 @@
         <v>1893</v>
       </c>
     </row>
-    <row r="360" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" s="1">
         <v>361</v>
       </c>
@@ -23177,7 +23178,7 @@
         <v>1898</v>
       </c>
     </row>
-    <row r="361" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" s="1">
         <v>362</v>
       </c>
@@ -23221,7 +23222,7 @@
         <v>1903</v>
       </c>
     </row>
-    <row r="362" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" s="1">
         <v>363</v>
       </c>
@@ -23265,7 +23266,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="363" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" s="1">
         <v>364</v>
       </c>
@@ -23309,7 +23310,7 @@
         <v>1913</v>
       </c>
     </row>
-    <row r="364" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" s="1">
         <v>365</v>
       </c>
@@ -23353,7 +23354,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="365" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" s="1">
         <v>366</v>
       </c>
@@ -23397,7 +23398,7 @@
         <v>1923</v>
       </c>
     </row>
-    <row r="366" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" s="1">
         <v>367</v>
       </c>
@@ -23441,7 +23442,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="367" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" s="1">
         <v>368</v>
       </c>
@@ -23485,7 +23486,7 @@
         <v>1931</v>
       </c>
     </row>
-    <row r="368" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" s="1">
         <v>369</v>
       </c>
@@ -23529,7 +23530,7 @@
         <v>1936</v>
       </c>
     </row>
-    <row r="369" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" s="1">
         <v>370</v>
       </c>
@@ -23573,7 +23574,7 @@
         <v>1941</v>
       </c>
     </row>
-    <row r="370" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" s="1">
         <v>371</v>
       </c>
@@ -23617,7 +23618,7 @@
         <v>1947</v>
       </c>
     </row>
-    <row r="371" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" s="1">
         <v>372</v>
       </c>
@@ -23661,7 +23662,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="372" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" s="1">
         <v>373</v>
       </c>
@@ -23705,7 +23706,7 @@
         <v>1957</v>
       </c>
     </row>
-    <row r="373" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" s="1">
         <v>374</v>
       </c>
@@ -23749,7 +23750,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="374" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" s="1">
         <v>375</v>
       </c>
@@ -23793,7 +23794,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="375" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" s="1">
         <v>376</v>
       </c>
@@ -23837,7 +23838,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="376" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" s="1">
         <v>377</v>
       </c>
@@ -23881,7 +23882,7 @@
         <v>1976</v>
       </c>
     </row>
-    <row r="377" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" s="1">
         <v>378</v>
       </c>
@@ -23925,7 +23926,7 @@
         <v>1981</v>
       </c>
     </row>
-    <row r="378" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" s="1">
         <v>379</v>
       </c>
@@ -23969,7 +23970,7 @@
         <v>1986</v>
       </c>
     </row>
-    <row r="379" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" s="1">
         <v>380</v>
       </c>
@@ -24013,7 +24014,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="380" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" s="1">
         <v>381</v>
       </c>
@@ -24057,7 +24058,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="381" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" s="1">
         <v>382</v>
       </c>
@@ -24101,7 +24102,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="382" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" s="1">
         <v>383</v>
       </c>
@@ -24145,7 +24146,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="383" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" s="1">
         <v>384</v>
       </c>
@@ -24189,7 +24190,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="384" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" s="1">
         <v>385</v>
       </c>
@@ -24233,7 +24234,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="385" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" s="1">
         <v>386</v>
       </c>
@@ -24277,7 +24278,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="386" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" s="1">
         <v>387</v>
       </c>
@@ -24321,7 +24322,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="387" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" s="1">
         <v>388</v>
       </c>
@@ -24365,7 +24366,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="388" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" s="1">
         <v>389</v>
       </c>
@@ -24409,7 +24410,7 @@
         <v>2036</v>
       </c>
     </row>
-    <row r="389" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" s="1">
         <v>390</v>
       </c>
@@ -24453,7 +24454,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="390" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" s="1">
         <v>391</v>
       </c>
@@ -24464,7 +24465,7 @@
         <v>2043</v>
       </c>
       <c r="D390" s="1" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="E390" s="1">
         <v>934116972425</v>
@@ -24497,7 +24498,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="391" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" s="1">
         <v>392</v>
       </c>
@@ -24541,7 +24542,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="392" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" s="1">
         <v>393</v>
       </c>
@@ -24585,7 +24586,7 @@
         <v>2057</v>
       </c>
     </row>
-    <row r="393" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" s="1">
         <v>394</v>
       </c>
@@ -24629,7 +24630,7 @@
         <v>2063</v>
       </c>
     </row>
-    <row r="394" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" s="1">
         <v>395</v>
       </c>
@@ -24673,7 +24674,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="395" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" s="1">
         <v>396</v>
       </c>
@@ -24717,7 +24718,7 @@
         <v>2075</v>
       </c>
     </row>
-    <row r="396" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" s="1">
         <v>397</v>
       </c>
@@ -24761,7 +24762,7 @@
         <v>2081</v>
       </c>
     </row>
-    <row r="397" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" s="1">
         <v>398</v>
       </c>
@@ -24799,13 +24800,13 @@
         <v>28120305828</v>
       </c>
       <c r="M397" s="1" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="N397" s="1" t="s">
         <v>2086</v>
       </c>
     </row>
-    <row r="398" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" s="1">
         <v>399</v>
       </c>
@@ -24849,7 +24850,7 @@
         <v>2092</v>
       </c>
     </row>
-    <row r="399" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" s="1">
         <v>400</v>
       </c>
@@ -24893,7 +24894,7 @@
         <v>2098</v>
       </c>
     </row>
-    <row r="400" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" s="1">
         <v>401</v>
       </c>
@@ -24937,7 +24938,7 @@
         <v>2104</v>
       </c>
     </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" s="1">
         <v>402</v>
       </c>
@@ -24981,7 +24982,7 @@
         <v>2108</v>
       </c>
     </row>
-    <row r="402" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" s="1">
         <v>403</v>
       </c>
@@ -25025,7 +25026,7 @@
         <v>2114</v>
       </c>
     </row>
-    <row r="403" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" s="1">
         <v>404</v>
       </c>
@@ -25069,7 +25070,7 @@
         <v>2120</v>
       </c>
     </row>
-    <row r="404" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" s="1">
         <v>405</v>
       </c>
@@ -25113,7 +25114,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="405" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" s="1">
         <v>406</v>
       </c>
@@ -25157,7 +25158,7 @@
         <v>2128</v>
       </c>
     </row>
-    <row r="406" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406" s="1">
         <v>407</v>
       </c>
@@ -25168,7 +25169,7 @@
         <v>2129</v>
       </c>
       <c r="D406" s="1" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
       <c r="E406" s="1">
         <v>478239648089</v>
@@ -25201,7 +25202,7 @@
         <v>2133</v>
       </c>
     </row>
-    <row r="407" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407" s="1">
         <v>408</v>
       </c>
@@ -25245,7 +25246,7 @@
         <v>2139</v>
       </c>
     </row>
-    <row r="408" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408" s="1">
         <v>409</v>
       </c>
@@ -25289,7 +25290,7 @@
         <v>2146</v>
       </c>
     </row>
-    <row r="409" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" s="1">
         <v>410</v>
       </c>
@@ -25333,7 +25334,7 @@
         <v>2151</v>
       </c>
     </row>
-    <row r="410" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" s="1">
         <v>411</v>
       </c>
@@ -25377,7 +25378,7 @@
         <v>2156</v>
       </c>
     </row>
-    <row r="411" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" s="1">
         <v>412</v>
       </c>
@@ -25421,7 +25422,7 @@
         <v>2161</v>
       </c>
     </row>
-    <row r="412" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" s="1">
         <v>413</v>
       </c>
@@ -25465,7 +25466,7 @@
         <v>2166</v>
       </c>
     </row>
-    <row r="413" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413" s="1">
         <v>414</v>
       </c>
@@ -25509,7 +25510,7 @@
         <v>2171</v>
       </c>
     </row>
-    <row r="414" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414" s="1">
         <v>415</v>
       </c>
@@ -25553,7 +25554,7 @@
         <v>2176</v>
       </c>
     </row>
-    <row r="415" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415" s="1">
         <v>416</v>
       </c>
@@ -25597,7 +25598,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="416" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416" s="1">
         <v>417</v>
       </c>
@@ -25641,7 +25642,7 @@
         <v>2186</v>
       </c>
     </row>
-    <row r="417" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" s="1">
         <v>418</v>
       </c>
@@ -25685,7 +25686,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="418" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" s="1">
         <v>419</v>
       </c>
@@ -25729,7 +25730,7 @@
         <v>2196</v>
       </c>
     </row>
-    <row r="419" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" s="1">
         <v>420</v>
       </c>
@@ -25773,7 +25774,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="420" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420" s="1">
         <v>421</v>
       </c>
@@ -25817,7 +25818,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="421" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" s="1">
         <v>422</v>
       </c>
@@ -25861,7 +25862,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="422" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422" s="1">
         <v>424</v>
       </c>
@@ -25905,7 +25906,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="423" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423" s="1">
         <v>425</v>
       </c>
@@ -25949,7 +25950,7 @@
         <v>2216</v>
       </c>
     </row>
-    <row r="424" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424" s="1">
         <v>426</v>
       </c>
@@ -25993,7 +25994,7 @@
         <v>2221</v>
       </c>
     </row>
-    <row r="425" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425" s="1">
         <v>427</v>
       </c>
@@ -26037,7 +26038,7 @@
         <v>2226</v>
       </c>
     </row>
-    <row r="426" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" s="1">
         <v>428</v>
       </c>
@@ -26081,7 +26082,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="427" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" s="1">
         <v>429</v>
       </c>
@@ -26125,7 +26126,7 @@
         <v>2236</v>
       </c>
     </row>
-    <row r="428" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" s="1">
         <v>430</v>
       </c>
@@ -26169,7 +26170,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="429" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" s="1">
         <v>431</v>
       </c>
@@ -26213,7 +26214,7 @@
         <v>2246</v>
       </c>
     </row>
-    <row r="430" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430" s="1">
         <v>432</v>
       </c>
@@ -26224,7 +26225,7 @@
         <v>2247</v>
       </c>
       <c r="D430" s="1" t="s">
-        <v>2248</v>
+        <v>2296</v>
       </c>
       <c r="E430" s="1">
         <v>229227360459</v>
@@ -26236,7 +26237,7 @@
         <v>92</v>
       </c>
       <c r="H430" s="1" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="I430" s="1" t="s">
         <v>2211</v>
@@ -26251,13 +26252,13 @@
         <v>28112600218</v>
       </c>
       <c r="M430" s="1" t="s">
+        <v>2249</v>
+      </c>
+      <c r="N430" s="1" t="s">
         <v>2250</v>
       </c>
-      <c r="N430" s="1" t="s">
-        <v>2251</v>
-      </c>
-    </row>
-    <row r="431" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="431" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431" s="1">
         <v>433</v>
       </c>
@@ -26265,10 +26266,10 @@
         <v>240407411</v>
       </c>
       <c r="C431" s="1" t="s">
+        <v>2251</v>
+      </c>
+      <c r="D431" s="1" t="s">
         <v>2252</v>
-      </c>
-      <c r="D431" s="1" t="s">
-        <v>2253</v>
       </c>
       <c r="E431" s="1">
         <v>968497188057</v>
@@ -26280,7 +26281,7 @@
         <v>92</v>
       </c>
       <c r="H431" s="1" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="I431" s="1" t="s">
         <v>2211</v>
@@ -26295,13 +26296,13 @@
         <v>28112600218</v>
       </c>
       <c r="M431" s="1" t="s">
+        <v>2254</v>
+      </c>
+      <c r="N431" s="1" t="s">
         <v>2255</v>
       </c>
-      <c r="N431" s="1" t="s">
-        <v>2256</v>
-      </c>
-    </row>
-    <row r="432" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="432" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432" s="1">
         <v>434</v>
       </c>
@@ -26309,10 +26310,10 @@
         <v>240705820</v>
       </c>
       <c r="C432" s="1" t="s">
+        <v>2256</v>
+      </c>
+      <c r="D432" s="1" t="s">
         <v>2257</v>
-      </c>
-      <c r="D432" s="1" t="s">
-        <v>2258</v>
       </c>
       <c r="E432" s="1">
         <v>878002394991</v>
@@ -26324,7 +26325,7 @@
         <v>103</v>
       </c>
       <c r="H432" s="1" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="I432" s="1" t="s">
         <v>2211</v>
@@ -26339,13 +26340,13 @@
         <v>28112600218</v>
       </c>
       <c r="M432" s="1" t="s">
+        <v>2259</v>
+      </c>
+      <c r="N432" s="1" t="s">
         <v>2260</v>
       </c>
-      <c r="N432" s="1" t="s">
-        <v>2261</v>
-      </c>
-    </row>
-    <row r="433" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="433" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" s="1">
         <v>435</v>
       </c>
@@ -26353,10 +26354,10 @@
         <v>240809046</v>
       </c>
       <c r="C433" s="1" t="s">
+        <v>2261</v>
+      </c>
+      <c r="D433" s="1" t="s">
         <v>2262</v>
-      </c>
-      <c r="D433" s="1" t="s">
-        <v>2263</v>
       </c>
       <c r="E433" s="1">
         <v>586911867031</v>
@@ -26368,7 +26369,7 @@
         <v>109</v>
       </c>
       <c r="H433" s="1" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="I433" s="1" t="s">
         <v>2211</v>
@@ -26383,10 +26384,10 @@
         <v>28112600218</v>
       </c>
       <c r="M433" s="1" t="s">
+        <v>2264</v>
+      </c>
+      <c r="N433" s="1" t="s">
         <v>2265</v>
-      </c>
-      <c r="N433" s="1" t="s">
-        <v>2266</v>
       </c>
     </row>
     <row r="434" spans="1:14" x14ac:dyDescent="0.3">
@@ -26397,7 +26398,7 @@
         <v>241408099</v>
       </c>
       <c r="C434" s="1" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="D434" s="1" t="s">
         <v>1177</v>
@@ -26412,7 +26413,7 @@
         <v>121</v>
       </c>
       <c r="H434" s="1">
-        <v>829504261</v>
+        <v>8295304261</v>
       </c>
       <c r="I434" s="1" t="s">
         <v>2211</v>
@@ -26427,21 +26428,21 @@
         <v>28112600218</v>
       </c>
       <c r="M434" s="1" t="s">
+        <v>2267</v>
+      </c>
+      <c r="N434" s="1" t="s">
         <v>2268</v>
       </c>
-      <c r="N434" s="1" t="s">
-        <v>2269</v>
-      </c>
-    </row>
-    <row r="435" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="435" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435" s="1">
         <v>437</v>
       </c>
       <c r="B435" s="1">
-        <v>24108329</v>
+        <v>241408329</v>
       </c>
       <c r="C435" s="1" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="D435" s="1" t="s">
         <v>1632</v>
@@ -26471,13 +26472,13 @@
         <v>28112600218</v>
       </c>
       <c r="M435" s="1" t="s">
+        <v>2270</v>
+      </c>
+      <c r="N435" s="1" t="s">
         <v>2271</v>
       </c>
-      <c r="N435" s="1" t="s">
-        <v>2272</v>
-      </c>
-    </row>
-    <row r="436" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="436" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436" s="1">
         <v>438</v>
       </c>
@@ -26485,10 +26486,10 @@
         <v>240405480</v>
       </c>
       <c r="C436" s="1" t="s">
+        <v>2272</v>
+      </c>
+      <c r="D436" s="1" t="s">
         <v>2273</v>
-      </c>
-      <c r="D436" s="1" t="s">
-        <v>2274</v>
       </c>
       <c r="E436" s="1">
         <v>672636872063</v>
@@ -26500,7 +26501,7 @@
         <v>1750</v>
       </c>
       <c r="H436" s="1" t="s">
-        <v>2275</v>
+        <v>2274</v>
       </c>
       <c r="I436" s="1" t="s">
         <v>2143</v>
@@ -26515,13 +26516,13 @@
         <v>28111401524</v>
       </c>
       <c r="M436" s="1" t="s">
+        <v>2275</v>
+      </c>
+      <c r="N436" s="1" t="s">
         <v>2276</v>
       </c>
-      <c r="N436" s="1" t="s">
-        <v>2277</v>
-      </c>
-    </row>
-    <row r="437" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="437" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437" s="1">
         <v>439</v>
       </c>
@@ -26529,10 +26530,10 @@
         <v>241801185</v>
       </c>
       <c r="C437" s="1" t="s">
+        <v>2277</v>
+      </c>
+      <c r="D437" s="1" t="s">
         <v>2278</v>
-      </c>
-      <c r="D437" s="1" t="s">
-        <v>2279</v>
       </c>
       <c r="E437" s="1">
         <v>205744368365</v>
@@ -26544,7 +26545,7 @@
         <v>132</v>
       </c>
       <c r="H437" s="1" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="I437" s="1" t="s">
         <v>2211</v>
@@ -26559,13 +26560,13 @@
         <v>28112600218</v>
       </c>
       <c r="M437" s="1" t="s">
+        <v>2280</v>
+      </c>
+      <c r="N437" s="1" t="s">
         <v>2281</v>
       </c>
-      <c r="N437" s="1" t="s">
-        <v>2282</v>
-      </c>
-    </row>
-    <row r="438" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="438" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" s="1">
         <v>478</v>
       </c>
@@ -26573,22 +26574,22 @@
         <v>240302549</v>
       </c>
       <c r="C438" s="1" t="s">
+        <v>2282</v>
+      </c>
+      <c r="D438" s="1" t="s">
         <v>2283</v>
       </c>
-      <c r="D438" s="1" t="s">
+      <c r="E438" s="1" t="s">
         <v>2284</v>
-      </c>
-      <c r="E438" s="1" t="s">
-        <v>2285</v>
       </c>
       <c r="F438" s="1" t="s">
         <v>74</v>
       </c>
       <c r="G438" s="1" t="s">
+        <v>2285</v>
+      </c>
+      <c r="H438" s="1" t="s">
         <v>2286</v>
-      </c>
-      <c r="H438" s="1" t="s">
-        <v>2287</v>
       </c>
       <c r="I438" s="1" t="s">
         <v>2211</v>
@@ -26603,13 +26604,20 @@
         <v>28112600218</v>
       </c>
       <c r="M438" s="1" t="s">
+        <v>2287</v>
+      </c>
+      <c r="N438" s="1" t="s">
         <v>2288</v>
       </c>
-      <c r="N438" s="1" t="s">
-        <v>2289</v>
-      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N438" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="2608LPT027"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>

--- a/students.xlsx
+++ b/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hallticket download\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFFD86FA-B017-4F07-8359-7017E9D632D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34FF71D1-0293-4B4F-A6CF-71412E956D60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4364" uniqueCount="2297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4361" uniqueCount="2297">
   <si>
     <t>S.No.</t>
   </si>
@@ -8531,7 +8531,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="1">
-        <v>240404885</v>
+        <v>240403885</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>172</v>
@@ -12310,7 +12310,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="114" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>115</v>
       </c>
@@ -12354,7 +12354,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="115" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>116</v>
       </c>
@@ -12398,7 +12398,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="116" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>117</v>
       </c>
@@ -12442,7 +12442,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="117" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>118</v>
       </c>
@@ -12486,7 +12486,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="118" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>119</v>
       </c>
@@ -12508,8 +12508,8 @@
       <c r="G118" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H118" s="1" t="s">
-        <v>537</v>
+      <c r="H118" s="1">
+        <v>9919984407</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>632</v>
@@ -12530,7 +12530,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="119" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>120</v>
       </c>
@@ -12574,7 +12574,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="120" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>121</v>
       </c>
@@ -12618,7 +12618,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="121" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>122</v>
       </c>
@@ -12662,7 +12662,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="122" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>123</v>
       </c>
@@ -12706,7 +12706,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="123" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>124</v>
       </c>
@@ -12750,7 +12750,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="124" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>125</v>
       </c>
@@ -12794,7 +12794,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="125" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>126</v>
       </c>
@@ -12838,7 +12838,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="126" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>127</v>
       </c>
@@ -12882,7 +12882,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="127" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>128</v>
       </c>
@@ -12926,7 +12926,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="128" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>129</v>
       </c>
@@ -12970,7 +12970,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="129" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>130</v>
       </c>
@@ -13014,7 +13014,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="130" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>131</v>
       </c>
@@ -13058,7 +13058,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="131" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>132</v>
       </c>
@@ -13102,7 +13102,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="132" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>133</v>
       </c>
@@ -13124,8 +13124,8 @@
       <c r="G132" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="H132" s="1" t="s">
-        <v>711</v>
+      <c r="H132" s="1">
+        <v>9728146886</v>
       </c>
       <c r="I132" s="1" t="s">
         <v>632</v>
@@ -13146,7 +13146,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="133" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>134</v>
       </c>
@@ -13168,8 +13168,8 @@
       <c r="G133" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="H133" s="1" t="s">
-        <v>722</v>
+      <c r="H133" s="1">
+        <v>9870975865</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>632</v>
@@ -13190,7 +13190,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="134" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>135</v>
       </c>
@@ -26390,7 +26390,7 @@
         <v>2265</v>
       </c>
     </row>
-    <row r="434" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" s="1">
         <v>436</v>
       </c>
@@ -26612,9 +26612,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:N438" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="2">
+    <filterColumn colId="8">
       <filters>
-        <filter val="2608LPT027"/>
+        <filter val="EMRS Y. RAMAVARAM, VILL- P. YERRAGONDA, MANDAL- Y. RAMAVARAM, POLAVARAM DIST. A.P PIN- 533483"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/students.xlsx
+++ b/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hallticket download\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34FF71D1-0293-4B4F-A6CF-71412E956D60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C59E45-EBCE-41B2-B298-1EFBB1A043E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4361" uniqueCount="2297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4360" uniqueCount="2297">
   <si>
     <t>S.No.</t>
   </si>
@@ -13080,8 +13080,8 @@
       <c r="G131" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H131" s="1" t="s">
-        <v>537</v>
+      <c r="H131" s="1">
+        <v>7210003518</v>
       </c>
       <c r="I131" s="1" t="s">
         <v>632</v>
